--- a/output/pdf_financials_xlsx/MFA.P.xlsx
+++ b/output/pdf_financials_xlsx/MFA.P.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.013884</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.007868</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001964</v>
       </c>
     </row>
     <row r="13">
@@ -1029,13 +1029,13 @@
         <v>-0.200239</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.136852</v>
+        <v>-0.150736</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.099343</v>
+        <v>-0.107211</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.159395</v>
+        <v>-0.161359</v>
       </c>
     </row>
     <row r="28">
@@ -1073,13 +1073,13 @@
         <v>-0.200239</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.136852</v>
+        <v>-0.150736</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.099343</v>
+        <v>-0.107211</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.159395</v>
+        <v>-0.161359</v>
       </c>
     </row>
     <row r="30">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">

--- a/output/pdf_financials_xlsx/MFA.P.xlsx
+++ b/output/pdf_financials_xlsx/MFA.P.xlsx
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.206833</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -6488,7 +6488,11 @@
           <t>Issuance of common shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>0.206833</v>
       </c>

--- a/output/pdf_financials_xlsx/MFA.P.xlsx
+++ b/output/pdf_financials_xlsx/MFA.P.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.01745</v>
+        <v>0.020332</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.09222</v>
+        <v>0.103738</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.11619</v>
+        <v>0.128805</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.063212</v>
+        <v>0.08067000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.123901</v>
+        <v>0.143605</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.01745</v>
+        <v>0.020332</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.200239</v>
@@ -634,10 +634,10 @@
         <v>0.150736</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.063212</v>
+        <v>0.08067000000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.123901</v>
+        <v>0.143605</v>
       </c>
     </row>
     <row r="11">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.01745</v>
+        <v>-0.020332</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.200239</v>
@@ -656,10 +656,10 @@
         <v>-0.150736</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.063212</v>
+        <v>-0.08067000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.123901</v>
+        <v>-0.143605</v>
       </c>
     </row>
     <row r="12">
@@ -6742,7 +6742,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>0.206833</v>
       </c>
@@ -7006,7 +7010,11 @@
           <t>General and office expenses (Note 7)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>0.002882</v>
       </c>
@@ -7601,7 +7609,11 @@
           <t>General and office expenses (Note 8)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>0.002882</v>
       </c>
